--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\PythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_AE6C94CD181A383656B8BAB57AAA3F03C8F4A117" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C214FDC5-06F6-4F7F-B9BD-ED9E92A9ABDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2804" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2950" uniqueCount="696">
   <si>
     <t>university</t>
   </si>
@@ -2453,15 +2453,15 @@
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="119.6640625" customWidth="1"/>
-    <col min="5" max="5" width="49.109375" customWidth="1"/>
+    <col min="4" max="4" width="202.77734375" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="35" customWidth="1"/>
+    <col min="13" max="13" width="102.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -2603,6 +2603,9 @@
       <c r="E4" t="s">
         <v>17</v>
       </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4">
         <v>158100</v>
       </c>
@@ -2884,6 +2887,9 @@
       <c r="E11" t="s">
         <v>33</v>
       </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
       <c r="G11">
         <v>94900</v>
       </c>
@@ -3405,6 +3411,9 @@
       <c r="E24" t="s">
         <v>55</v>
       </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
       <c r="G24">
         <v>158100</v>
       </c>
@@ -3686,6 +3695,9 @@
       <c r="E31" t="s">
         <v>68</v>
       </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
       <c r="G31">
         <v>158100</v>
       </c>
@@ -3803,6 +3815,9 @@
       <c r="E34" t="s">
         <v>68</v>
       </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
       <c r="G34">
         <v>94900</v>
       </c>
@@ -3876,6 +3891,9 @@
       <c r="E36" t="s">
         <v>80</v>
       </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
       <c r="G36">
         <v>288000</v>
       </c>
@@ -3952,6 +3970,9 @@
       <c r="E38" t="s">
         <v>80</v>
       </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
       <c r="G38">
         <v>288000</v>
       </c>
@@ -4110,6 +4131,9 @@
       <c r="E42" t="s">
         <v>80</v>
       </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
       <c r="G42">
         <v>84100</v>
       </c>
@@ -4227,6 +4251,9 @@
       <c r="E45" t="s">
         <v>99</v>
       </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
       <c r="G45">
         <v>158100</v>
       </c>
@@ -4833,6 +4860,9 @@
       <c r="E60" t="s">
         <v>131</v>
       </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
       <c r="G60">
         <v>205400</v>
       </c>
@@ -6226,6 +6256,12 @@
       <c r="I95" t="s">
         <v>18</v>
       </c>
+      <c r="J95" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95" t="s">
+        <v>19</v>
+      </c>
       <c r="L95">
         <v>6</v>
       </c>
@@ -6261,6 +6297,12 @@
       <c r="I96" t="s">
         <v>18</v>
       </c>
+      <c r="J96" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" t="s">
+        <v>19</v>
+      </c>
       <c r="L96">
         <v>3</v>
       </c>
@@ -6296,6 +6338,12 @@
       <c r="I97" t="s">
         <v>18</v>
       </c>
+      <c r="J97" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" t="s">
+        <v>19</v>
+      </c>
       <c r="L97">
         <v>20</v>
       </c>
@@ -6328,6 +6376,15 @@
       <c r="I98" t="s">
         <v>18</v>
       </c>
+      <c r="J98" t="s">
+        <v>18</v>
+      </c>
+      <c r="K98" t="s">
+        <v>19</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
       <c r="M98" t="s">
         <v>206</v>
       </c>
@@ -6357,6 +6414,15 @@
       <c r="I99" t="s">
         <v>18</v>
       </c>
+      <c r="J99" t="s">
+        <v>18</v>
+      </c>
+      <c r="K99" t="s">
+        <v>19</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
       <c r="M99" t="s">
         <v>206</v>
       </c>
@@ -6389,6 +6455,12 @@
       <c r="I100" t="s">
         <v>18</v>
       </c>
+      <c r="J100" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100" t="s">
+        <v>19</v>
+      </c>
       <c r="L100">
         <v>8</v>
       </c>
@@ -6424,6 +6496,12 @@
       <c r="I101" t="s">
         <v>18</v>
       </c>
+      <c r="J101" t="s">
+        <v>18</v>
+      </c>
+      <c r="K101" t="s">
+        <v>19</v>
+      </c>
       <c r="L101">
         <v>4</v>
       </c>
@@ -6459,6 +6537,12 @@
       <c r="I102" t="s">
         <v>18</v>
       </c>
+      <c r="J102" t="s">
+        <v>18</v>
+      </c>
+      <c r="K102" t="s">
+        <v>19</v>
+      </c>
       <c r="L102">
         <v>4</v>
       </c>
@@ -6494,6 +6578,12 @@
       <c r="I103" t="s">
         <v>18</v>
       </c>
+      <c r="J103" t="s">
+        <v>18</v>
+      </c>
+      <c r="K103" t="s">
+        <v>19</v>
+      </c>
       <c r="L103">
         <v>2</v>
       </c>
@@ -6529,6 +6619,12 @@
       <c r="I104" t="s">
         <v>18</v>
       </c>
+      <c r="J104" t="s">
+        <v>18</v>
+      </c>
+      <c r="K104" t="s">
+        <v>19</v>
+      </c>
       <c r="L104">
         <v>4</v>
       </c>
@@ -6564,6 +6660,12 @@
       <c r="I105" t="s">
         <v>18</v>
       </c>
+      <c r="J105" t="s">
+        <v>18</v>
+      </c>
+      <c r="K105" t="s">
+        <v>19</v>
+      </c>
       <c r="L105">
         <v>3</v>
       </c>
@@ -6599,6 +6701,12 @@
       <c r="I106" t="s">
         <v>18</v>
       </c>
+      <c r="J106" t="s">
+        <v>18</v>
+      </c>
+      <c r="K106" t="s">
+        <v>19</v>
+      </c>
       <c r="L106">
         <v>2</v>
       </c>
@@ -6634,6 +6742,12 @@
       <c r="I107" t="s">
         <v>18</v>
       </c>
+      <c r="J107" t="s">
+        <v>18</v>
+      </c>
+      <c r="K107" t="s">
+        <v>19</v>
+      </c>
       <c r="L107">
         <v>5</v>
       </c>
@@ -6669,6 +6783,12 @@
       <c r="I108" t="s">
         <v>18</v>
       </c>
+      <c r="J108" t="s">
+        <v>18</v>
+      </c>
+      <c r="K108" t="s">
+        <v>19</v>
+      </c>
       <c r="L108">
         <v>13</v>
       </c>
@@ -6704,6 +6824,12 @@
       <c r="I109" t="s">
         <v>18</v>
       </c>
+      <c r="J109" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109" t="s">
+        <v>19</v>
+      </c>
       <c r="L109">
         <v>16</v>
       </c>
@@ -6736,6 +6862,15 @@
       <c r="I110" t="s">
         <v>18</v>
       </c>
+      <c r="J110" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110" t="s">
+        <v>19</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
       <c r="M110" t="s">
         <v>233</v>
       </c>
@@ -6765,6 +6900,15 @@
       <c r="I111" t="s">
         <v>18</v>
       </c>
+      <c r="J111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111" t="s">
+        <v>19</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
       <c r="M111" t="s">
         <v>233</v>
       </c>
@@ -6794,6 +6938,12 @@
       <c r="I112" t="s">
         <v>18</v>
       </c>
+      <c r="J112" t="s">
+        <v>18</v>
+      </c>
+      <c r="K112" t="s">
+        <v>19</v>
+      </c>
       <c r="L112">
         <v>3</v>
       </c>
@@ -6829,6 +6979,12 @@
       <c r="I113" t="s">
         <v>18</v>
       </c>
+      <c r="J113" t="s">
+        <v>18</v>
+      </c>
+      <c r="K113" t="s">
+        <v>19</v>
+      </c>
       <c r="L113">
         <v>8</v>
       </c>
@@ -6864,6 +7020,12 @@
       <c r="I114" t="s">
         <v>18</v>
       </c>
+      <c r="J114" t="s">
+        <v>18</v>
+      </c>
+      <c r="K114" t="s">
+        <v>19</v>
+      </c>
       <c r="L114">
         <v>5</v>
       </c>
@@ -6899,6 +7061,12 @@
       <c r="I115" t="s">
         <v>18</v>
       </c>
+      <c r="J115" t="s">
+        <v>18</v>
+      </c>
+      <c r="K115" t="s">
+        <v>19</v>
+      </c>
       <c r="L115">
         <v>8</v>
       </c>
@@ -6928,6 +7096,15 @@
       <c r="I116" t="s">
         <v>18</v>
       </c>
+      <c r="J116" t="s">
+        <v>18</v>
+      </c>
+      <c r="K116" t="s">
+        <v>19</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
       <c r="M116" t="s">
         <v>206</v>
       </c>
@@ -6960,6 +7137,12 @@
       <c r="I117" t="s">
         <v>18</v>
       </c>
+      <c r="J117" t="s">
+        <v>18</v>
+      </c>
+      <c r="K117" t="s">
+        <v>19</v>
+      </c>
       <c r="L117">
         <v>8</v>
       </c>
@@ -6995,6 +7178,12 @@
       <c r="I118" t="s">
         <v>18</v>
       </c>
+      <c r="J118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118" t="s">
+        <v>19</v>
+      </c>
       <c r="L118">
         <v>10</v>
       </c>
@@ -7030,6 +7219,12 @@
       <c r="I119" t="s">
         <v>18</v>
       </c>
+      <c r="J119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119" t="s">
+        <v>19</v>
+      </c>
       <c r="L119">
         <v>6</v>
       </c>
@@ -7065,6 +7260,12 @@
       <c r="I120" t="s">
         <v>18</v>
       </c>
+      <c r="J120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120" t="s">
+        <v>19</v>
+      </c>
       <c r="L120">
         <v>6</v>
       </c>
@@ -7100,6 +7301,12 @@
       <c r="I121" t="s">
         <v>18</v>
       </c>
+      <c r="J121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121" t="s">
+        <v>19</v>
+      </c>
       <c r="L121">
         <v>4</v>
       </c>
@@ -7135,6 +7342,12 @@
       <c r="I122" t="s">
         <v>18</v>
       </c>
+      <c r="J122" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122" t="s">
+        <v>19</v>
+      </c>
       <c r="L122">
         <v>6</v>
       </c>
@@ -7167,6 +7380,15 @@
       <c r="I123" t="s">
         <v>18</v>
       </c>
+      <c r="J123" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123" t="s">
+        <v>19</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
       <c r="M123" t="s">
         <v>248</v>
       </c>
@@ -7196,6 +7418,15 @@
       <c r="I124" t="s">
         <v>18</v>
       </c>
+      <c r="J124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124" t="s">
+        <v>19</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
       <c r="M124" t="s">
         <v>248</v>
       </c>
@@ -7228,6 +7459,12 @@
       <c r="I125" t="s">
         <v>18</v>
       </c>
+      <c r="J125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125" t="s">
+        <v>19</v>
+      </c>
       <c r="L125">
         <v>5</v>
       </c>
@@ -7263,6 +7500,12 @@
       <c r="I126" t="s">
         <v>18</v>
       </c>
+      <c r="J126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126" t="s">
+        <v>19</v>
+      </c>
       <c r="L126">
         <v>3</v>
       </c>
@@ -7295,6 +7538,15 @@
       <c r="I127" t="s">
         <v>18</v>
       </c>
+      <c r="J127" t="s">
+        <v>18</v>
+      </c>
+      <c r="K127" t="s">
+        <v>19</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
       <c r="M127" t="s">
         <v>257</v>
       </c>
@@ -7327,6 +7579,12 @@
       <c r="I128" t="s">
         <v>18</v>
       </c>
+      <c r="J128" t="s">
+        <v>18</v>
+      </c>
+      <c r="K128" t="s">
+        <v>19</v>
+      </c>
       <c r="L128">
         <v>8</v>
       </c>
@@ -7362,6 +7620,12 @@
       <c r="I129" t="s">
         <v>18</v>
       </c>
+      <c r="J129" t="s">
+        <v>18</v>
+      </c>
+      <c r="K129" t="s">
+        <v>19</v>
+      </c>
       <c r="L129">
         <v>10</v>
       </c>
@@ -7394,6 +7658,15 @@
       <c r="I130" t="s">
         <v>18</v>
       </c>
+      <c r="J130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130" t="s">
+        <v>19</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
       <c r="M130" t="s">
         <v>233</v>
       </c>
@@ -7426,6 +7699,12 @@
       <c r="I131" t="s">
         <v>18</v>
       </c>
+      <c r="J131" t="s">
+        <v>18</v>
+      </c>
+      <c r="K131" t="s">
+        <v>19</v>
+      </c>
       <c r="L131">
         <v>3</v>
       </c>
@@ -7461,6 +7740,12 @@
       <c r="I132" t="s">
         <v>18</v>
       </c>
+      <c r="J132" t="s">
+        <v>18</v>
+      </c>
+      <c r="K132" t="s">
+        <v>19</v>
+      </c>
       <c r="L132">
         <v>12</v>
       </c>
@@ -7496,6 +7781,12 @@
       <c r="I133" t="s">
         <v>18</v>
       </c>
+      <c r="J133" t="s">
+        <v>18</v>
+      </c>
+      <c r="K133" t="s">
+        <v>19</v>
+      </c>
       <c r="L133">
         <v>15</v>
       </c>
@@ -7531,6 +7822,12 @@
       <c r="I134" t="s">
         <v>18</v>
       </c>
+      <c r="J134" t="s">
+        <v>18</v>
+      </c>
+      <c r="K134" t="s">
+        <v>19</v>
+      </c>
       <c r="L134">
         <v>3</v>
       </c>
@@ -7563,8 +7860,14 @@
       <c r="I135" t="s">
         <v>18</v>
       </c>
+      <c r="J135" t="s">
+        <v>18</v>
+      </c>
       <c r="K135" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
       </c>
       <c r="M135" t="s">
         <v>275</v>
@@ -7598,6 +7901,12 @@
       <c r="I136" t="s">
         <v>18</v>
       </c>
+      <c r="J136" t="s">
+        <v>18</v>
+      </c>
+      <c r="K136" t="s">
+        <v>19</v>
+      </c>
       <c r="L136">
         <v>4</v>
       </c>
@@ -7633,6 +7942,12 @@
       <c r="I137" t="s">
         <v>18</v>
       </c>
+      <c r="J137" t="s">
+        <v>18</v>
+      </c>
+      <c r="K137" t="s">
+        <v>19</v>
+      </c>
       <c r="L137">
         <v>5</v>
       </c>
@@ -7665,6 +7980,15 @@
       <c r="I138" t="s">
         <v>18</v>
       </c>
+      <c r="J138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138" t="s">
+        <v>19</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
       <c r="M138" t="s">
         <v>280</v>
       </c>
@@ -7694,6 +8018,15 @@
       <c r="I139" t="s">
         <v>18</v>
       </c>
+      <c r="J139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139" t="s">
+        <v>19</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
       <c r="M139" t="s">
         <v>283</v>
       </c>
@@ -7723,8 +8056,14 @@
       <c r="I140" t="s">
         <v>18</v>
       </c>
+      <c r="J140" t="s">
+        <v>18</v>
+      </c>
       <c r="K140" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
       </c>
       <c r="M140" t="s">
         <v>283</v>
@@ -7758,6 +8097,12 @@
       <c r="I141" t="s">
         <v>18</v>
       </c>
+      <c r="J141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141" t="s">
+        <v>19</v>
+      </c>
       <c r="L141">
         <v>1</v>
       </c>
@@ -7793,6 +8138,12 @@
       <c r="I142" t="s">
         <v>18</v>
       </c>
+      <c r="J142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142" t="s">
+        <v>19</v>
+      </c>
       <c r="L142">
         <v>1</v>
       </c>
@@ -7825,6 +8176,15 @@
       <c r="I143" t="s">
         <v>18</v>
       </c>
+      <c r="J143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143" t="s">
+        <v>19</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
       <c r="M143" t="s">
         <v>286</v>
       </c>
@@ -7857,6 +8217,12 @@
       <c r="I144" t="s">
         <v>18</v>
       </c>
+      <c r="J144" t="s">
+        <v>18</v>
+      </c>
+      <c r="K144" t="s">
+        <v>19</v>
+      </c>
       <c r="L144">
         <v>6</v>
       </c>
@@ -7892,6 +8258,12 @@
       <c r="I145" t="s">
         <v>18</v>
       </c>
+      <c r="J145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145" t="s">
+        <v>19</v>
+      </c>
       <c r="L145">
         <v>4</v>
       </c>
@@ -7927,6 +8299,12 @@
       <c r="I146" t="s">
         <v>18</v>
       </c>
+      <c r="J146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146" t="s">
+        <v>19</v>
+      </c>
       <c r="L146">
         <v>1</v>
       </c>
@@ -7959,6 +8337,15 @@
       <c r="I147" t="s">
         <v>18</v>
       </c>
+      <c r="J147" t="s">
+        <v>18</v>
+      </c>
+      <c r="K147" t="s">
+        <v>19</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
       <c r="M147" t="s">
         <v>291</v>
       </c>
@@ -7988,6 +8375,15 @@
       <c r="I148" t="s">
         <v>18</v>
       </c>
+      <c r="J148" t="s">
+        <v>18</v>
+      </c>
+      <c r="K148" t="s">
+        <v>19</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
       <c r="M148" t="s">
         <v>291</v>
       </c>
@@ -8017,6 +8413,15 @@
       <c r="I149" t="s">
         <v>18</v>
       </c>
+      <c r="J149" t="s">
+        <v>18</v>
+      </c>
+      <c r="K149" t="s">
+        <v>19</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
       <c r="M149" t="s">
         <v>291</v>
       </c>
@@ -8049,6 +8454,12 @@
       <c r="I150" t="s">
         <v>18</v>
       </c>
+      <c r="J150" t="s">
+        <v>18</v>
+      </c>
+      <c r="K150" t="s">
+        <v>19</v>
+      </c>
       <c r="L150">
         <v>5</v>
       </c>
@@ -8084,6 +8495,12 @@
       <c r="I151" t="s">
         <v>18</v>
       </c>
+      <c r="J151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151" t="s">
+        <v>19</v>
+      </c>
       <c r="L151">
         <v>2</v>
       </c>
@@ -8119,6 +8536,12 @@
       <c r="I152" t="s">
         <v>18</v>
       </c>
+      <c r="J152" t="s">
+        <v>18</v>
+      </c>
+      <c r="K152" t="s">
+        <v>19</v>
+      </c>
       <c r="L152">
         <v>4</v>
       </c>
@@ -8154,6 +8577,12 @@
       <c r="I153" t="s">
         <v>18</v>
       </c>
+      <c r="J153" t="s">
+        <v>18</v>
+      </c>
+      <c r="K153" t="s">
+        <v>19</v>
+      </c>
       <c r="L153">
         <v>5</v>
       </c>
@@ -8189,6 +8618,12 @@
       <c r="I154" t="s">
         <v>18</v>
       </c>
+      <c r="J154" t="s">
+        <v>18</v>
+      </c>
+      <c r="K154" t="s">
+        <v>19</v>
+      </c>
       <c r="L154">
         <v>5</v>
       </c>
@@ -8224,6 +8659,12 @@
       <c r="I155" t="s">
         <v>18</v>
       </c>
+      <c r="J155" t="s">
+        <v>18</v>
+      </c>
+      <c r="K155" t="s">
+        <v>19</v>
+      </c>
       <c r="L155">
         <v>4</v>
       </c>
@@ -8256,6 +8697,15 @@
       <c r="I156" t="s">
         <v>18</v>
       </c>
+      <c r="J156" t="s">
+        <v>18</v>
+      </c>
+      <c r="K156" t="s">
+        <v>19</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
       <c r="M156" t="s">
         <v>310</v>
       </c>
@@ -8288,6 +8738,12 @@
       <c r="I157" t="s">
         <v>18</v>
       </c>
+      <c r="J157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157" t="s">
+        <v>19</v>
+      </c>
       <c r="L157">
         <v>3</v>
       </c>
@@ -8323,6 +8779,12 @@
       <c r="I158" t="s">
         <v>18</v>
       </c>
+      <c r="J158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158" t="s">
+        <v>19</v>
+      </c>
       <c r="L158">
         <v>4</v>
       </c>
@@ -8355,6 +8817,15 @@
       <c r="I159" t="s">
         <v>18</v>
       </c>
+      <c r="J159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159" t="s">
+        <v>19</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
       <c r="M159" t="s">
         <v>307</v>
       </c>
@@ -8387,6 +8858,12 @@
       <c r="I160" t="s">
         <v>18</v>
       </c>
+      <c r="J160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160" t="s">
+        <v>19</v>
+      </c>
       <c r="L160">
         <v>7</v>
       </c>
@@ -8419,6 +8896,15 @@
       <c r="I161" t="s">
         <v>18</v>
       </c>
+      <c r="J161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161" t="s">
+        <v>19</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
       <c r="M161" t="s">
         <v>318</v>
       </c>
@@ -8448,6 +8934,15 @@
       <c r="I162" t="s">
         <v>18</v>
       </c>
+      <c r="J162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162" t="s">
+        <v>19</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
       <c r="M162" t="s">
         <v>318</v>
       </c>
@@ -8480,6 +8975,12 @@
       <c r="I163" t="s">
         <v>18</v>
       </c>
+      <c r="J163" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163" t="s">
+        <v>19</v>
+      </c>
       <c r="L163">
         <v>5</v>
       </c>
@@ -8512,6 +9013,12 @@
       <c r="I164" t="s">
         <v>18</v>
       </c>
+      <c r="J164" t="s">
+        <v>18</v>
+      </c>
+      <c r="K164" t="s">
+        <v>19</v>
+      </c>
       <c r="L164">
         <v>2</v>
       </c>
@@ -8544,6 +9051,12 @@
       <c r="I165" t="s">
         <v>18</v>
       </c>
+      <c r="J165" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165" t="s">
+        <v>19</v>
+      </c>
       <c r="L165">
         <v>2</v>
       </c>
@@ -8576,6 +9089,12 @@
       <c r="I166" t="s">
         <v>18</v>
       </c>
+      <c r="J166" t="s">
+        <v>18</v>
+      </c>
+      <c r="K166" t="s">
+        <v>19</v>
+      </c>
       <c r="L166">
         <v>2</v>
       </c>
@@ -8608,6 +9127,15 @@
       <c r="I167" t="s">
         <v>18</v>
       </c>
+      <c r="J167" t="s">
+        <v>18</v>
+      </c>
+      <c r="K167" t="s">
+        <v>19</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
       <c r="M167" t="s">
         <v>326</v>
       </c>
@@ -8639,6 +9167,12 @@
       </c>
       <c r="I168" t="s">
         <v>18</v>
+      </c>
+      <c r="J168" t="s">
+        <v>18</v>
+      </c>
+      <c r="K168" t="s">
+        <v>19</v>
       </c>
       <c r="L168">
         <v>2</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0B7A7A-4CFD-4566-B209-F5F7F559C82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="1296" windowWidth="17280" windowHeight="11064" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
